--- a/data/trans_dic/IP1014-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1014-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen defectos del habla</t>
+          <t>Menores que padecen defectos del habla (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,73</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,48</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,06</t>
+          <t>0,13; 1,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,39</t>
+          <t>0,16; 1,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,87</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 2,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,19</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,84</t>
+          <t>0,32; 3,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,69</t>
+          <t>0,1; 1,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,53</t>
+          <t>0,0; 0,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,79</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,04</t>
+          <t>0,18; 0,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,28</t>
+          <t>0,27; 1,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,77</t>
+          <t>0,08; 0,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,59</t>
+          <t>0,1; 0,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,72</t>
+          <t>0,19; 0,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,42</t>
+          <t>0,04; 0,37</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen defectos del habla (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3946</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3611</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2786</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3249</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5331</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4861</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4518</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3568</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>642; 5818</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>795; 7067</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4767</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1362</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1362</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1280</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4535</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4166</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4555</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3422</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4702</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3886</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3619</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>563; 5496</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3227</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>360; 5050</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1339</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4041</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>6030</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2942</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4927</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1321; 6920</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2009; 9086</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>617; 5357</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1383; 8699</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2762; 11357</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>615; 5343</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1014-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1014-Edad-trans_dic.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,25</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,27</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,38</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,15</t>
+          <t>0,13; 1,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,41</t>
+          <t>0,13; 1,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
     </row>
@@ -913,17 +913,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,2</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 3,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,42</t>
+          <t>0,0; 2,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,03</t>
+          <t>0,0; 1,19</t>
         </is>
       </c>
     </row>
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,09</t>
+          <t>0,32; 2,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,45</t>
+          <t>0,16; 1,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,43</t>
+          <t>0,0; 0,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,7</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1133,32 +1133,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,96</t>
+          <t>0,19; 1,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,21</t>
+          <t>0,26; 1,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,72</t>
+          <t>0,08; 0,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,62</t>
+          <t>0,1; 0,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,78</t>
+          <t>0,22; 0,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,37</t>
+          <t>0,04; 0,41</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3946</t>
+          <t>0; 3331</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3611</t>
+          <t>0; 4036</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3249</t>
+          <t>0; 3850</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5331</t>
+          <t>0; 4934</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1595,32 +1595,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4861</t>
+          <t>0; 4763</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4518</t>
+          <t>0; 5039</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3568</t>
+          <t>0; 3592</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>642; 5818</t>
+          <t>639; 5439</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>795; 7067</t>
+          <t>654; 6678</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4767</t>
+          <t>0; 5106</t>
         </is>
       </c>
     </row>
@@ -1758,32 +1758,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4535</t>
+          <t>0; 3392</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4166</t>
+          <t>0; 4762</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4555</t>
+          <t>0; 4628</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3422</t>
+          <t>0; 3407</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4702</t>
+          <t>0; 4111</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3886</t>
+          <t>0; 4483</t>
         </is>
       </c>
     </row>
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3619</t>
+          <t>0; 3188</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>563; 5496</t>
+          <t>564; 4994</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3227</t>
+          <t>0; 3210</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>360; 5050</t>
+          <t>570; 5595</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2942</t>
+          <t>0; 3026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4927</t>
+          <t>0; 6325</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2084,32 +2084,32 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1321; 6920</t>
+          <t>1351; 8159</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2009; 9086</t>
+          <t>1957; 9254</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>617; 5357</t>
+          <t>619; 5246</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1383; 8699</t>
+          <t>1351; 8156</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2762; 11357</t>
+          <t>3190; 11708</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>615; 5343</t>
+          <t>617; 5873</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1014-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP1014-Edad-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,22 +625,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,52</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,07</t>
+          <t>0,13; 1,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,33</t>
+          <t>0,16; 1,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,42 +898,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,31</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -955,27 +955,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,32; 2,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,6</t>
+          <t>0,17; 1,69</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,19; 1,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,27; 1,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,08; 0,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,13</t>
+          <t>0,0; 0,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,24</t>
+          <t>0,0; 0,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,58</t>
+          <t>0,14; 0,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,8</t>
+          <t>0,18; 0,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,41</t>
+          <t>0,04; 0,42</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>705</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3500</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3331</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4036</t>
+          <t>0; 3939</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1374</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1447</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1374</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1447</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3850</t>
+          <t>0; 4825</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4934</t>
+          <t>0; 5189</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3618</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4763</t>
+          <t>0; 3000</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 5039</t>
+          <t>0; 6238</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3592</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>639; 5439</t>
+          <t>641; 5390</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>654; 6678</t>
+          <t>796; 6992</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5106</t>
+          <t>0; 3992</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>679</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3397</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4023</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4423</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3392</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4762</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4628</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3407</t>
+          <t>0; 3403</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4111</t>
+          <t>0; 4752</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4483</t>
+          <t>0; 4504</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1815,12 +1815,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>642</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3237</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>572; 5060</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3188</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>564; 4994</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3210</t>
+          <t>0; 3215</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>570; 5595</t>
+          <t>577; 5909</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4691</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>1339</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3399</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>4691</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1995</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3026</t>
+          <t>1347; 7549</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 6325</t>
+          <t>2035; 9563</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>594; 5701</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1351; 8159</t>
+          <t>0; 3590</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1957; 9254</t>
+          <t>0; 5560</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>619; 5246</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1351; 8156</t>
+          <t>1919; 8259</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>3190; 11708</t>
+          <t>2671; 10538</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>617; 5873</t>
+          <t>617; 6052</t>
         </is>
       </c>
     </row>
